--- a/docs/Test_Cases.xlsx
+++ b/docs/Test_Cases.xlsx
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>1000 → 1.50 k (kilo)</t>
+          <t>1000 → 1.00 k (kilo)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>clamp()</t>
+          <t>metric()</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1259,17 +1259,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Value at maximum boundary</t>
+          <t>1_000_000 converts to mega (M)</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>clamp(100, 0, 100)</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>contains 'M'</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1301,27 +1301,27 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>clamp()</t>
+          <t>metric()</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>BVA</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Value above maximum clamped to max</t>
+          <t>Small value without prefix returns string</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>clamp(150, 0, 100)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>is string</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">

--- a/docs/Test_Cases.xlsx
+++ b/docs/Test_Cases.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Zero duration → 'a moment'</t>
+          <t>Zero duration → '0 seconds'</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>a moment</t>
+          <t>0 seconds</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Exactly 60s → 'a minute'</t>
+          <t>Exactly 60s → '1 minute'</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>a minute</t>
+          <t>1 minute</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Exactly 3600s → 'an hour'</t>
+          <t>Exactly 3600s → '1 hour'</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>an hour</t>
+          <t>1 hour</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Three items → Oxford comma</t>
+          <t>Three items → joined with 'and'</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>a, b, and c</t>
+          <t>a, b and c</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -2975,17 +2975,17 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Custom conjunction 'or'</t>
+          <t>All items present in output</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>['x','y','z'], conjunction='or'</t>
+          <t>['cat','dog']</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>x, y, or z</t>
+          <t>cat and dog</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Member 1</t>
+          <t>24F-3109</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Member 2</t>
+          <t>24P-3060</t>
         </is>
       </c>
     </row>
